--- a/Lingvistik_proj/ausen-persuasion_head_lingvistik.xlsx
+++ b/Lingvistik_proj/ausen-persuasion_head_lingvistik.xlsx
@@ -425,111 +425,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U83"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Finding ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tree sentences</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Found word</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Lemma</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Designation</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Body category</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Name of work</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Before Nouns</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Before Adjektives</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Before Verbs</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Before Adverbs</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Before Pre- and postpositions</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Before Objects</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>After Nouns</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>After Adjektives</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>After Verbs</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>After Adverbs</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>After Pre- and postpositions</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>After Objects</t>
         </is>
@@ -538,94 +543,99 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ausen-emma_S_2341_L_1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>"That is what you have in your head, I know and what you would certainly say if my father were not by."</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>"Especially when one of those two is such a fanciful, troublesome creature!" said Emma playfully. "That is what you have in your head, I know and what you would certainly say if my father were not by." "I believe it is very true, my dear, indeed," said Mr. Woodhouse, with a sigh.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>head, father</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>have, know, say</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>certainly</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>in, by</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>ausen-emma_S_2727_L_2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Emma turned away her head, divided between tears and smiles.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>"But, Mr. Knightley, she is really very sorry to lose poor Miss Taylor, and I am sure she will miss her more than she thinks for." Emma turned away her head, divided between tears and smiles. "It is impossible that Emma should not miss such a companion," said Mr. Knightley.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>.</t>
@@ -633,74 +643,79 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>head, tears, smiles</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>turned, divided</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>between</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>ausen-emma_S_2936_L_3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Mr. Knightley shook his head at her.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>I made the match, you know, four years ago; and to have it take place, and be proved in the right, when so many people said Mr. Weston would never marry again, may comfort me for any thing." Mr. Knightley shook his head at her. Her father fondly replied, "Ah!</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>.</t>
@@ -708,70 +723,75 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>shook</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>ausen-emma_S_11884_L_4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Mr. Elton was the very person fixed on by Emma for driving the young farmer out of Harriet's head.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>She then repeated some warm personal praise which she had drawn from Mr. Elton, and now did full justice to; and Harriet blushed and smiled, and said she had always thought Mr. Elton very agreeable. Mr. Elton was the very person fixed on by Emma for driving the young farmer out of Harriet's head. She thought it would be an excellent match; and only too palpably desirable, natural, and probable, for her to have much merit in planning it.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>.</t>
@@ -779,74 +799,79 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>person, farmer, head</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>very, young</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>fixed, driving</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>on, by, for, out, of</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>ausen-emma_S_13694_L_5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>There is health, not merely in her bloom, but in her air, her head, her glance.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>what a bloom of full health, and such a pretty height and size; such a firm and upright figure! There is health, not merely in her bloom, but in her air, her head, her glance. One hears sometimes of a child being `the picture of health;' now, Emma always gives me the idea of being the complete picture of grown-up health.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>.</t>
@@ -854,74 +879,79 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>health, bloom, air, head, glance</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>is</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>merely</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>in, in</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>ausen-emma_S_16168_L_6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>He had nestled down his head most conveniently.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>I took him as he was sleeping on the sofa, and it is as strong a likeness of his cockade as you would wish to see. He had nestled down his head most conveniently. That's very like.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>.</t>
@@ -929,74 +959,79 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>nestled</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>most, conveniently</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>down</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>ausen-emma_S_24059_L_7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Vanity working on a weak head, produces every sort of mischief.</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>You will puff her up with such ideas of her own beauty, and of what she has a claim to, that, in a little while, nobody within her reach will be good enough for her. Vanity working on a weak head, produces every sort of mischief. Nothing so easy as for a young lady to raise her expectations too high.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>.</t>
@@ -1004,74 +1039,79 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Vanity, head, sort, mischief</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>weak</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>working, produces</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>on, of</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>ausen-emma_S_26305_L_8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Miss Nash, head-teacher at Mrs. Goddard's, had written out at least three hundred; and Harriet, who had taken the first hint of it from her, hoped, with Miss Woodhouse's help, to get a great many more.</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>In this age of literature, such collections on a very grand scale are not uncommon. Miss Nash, head-teacher at Mrs. Goddard's, had written out at least three hundred; and Harriet, who had taken the first hint of it from her, hoped, with Miss Woodhouse's help, to get a great many more. Emma assisted with her invention, memory and taste; and as Harriet wrote a very pretty hand, it was likely to be an arrangement of the first order, in form as well as quantity.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>.</t>
@@ -1079,78 +1119,83 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>head, teacher, hint, help</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>first, great, many, more</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>written, taken, hoped, get</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>at, least</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>at, out, of, from, with</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>ausen-emma_S_35885_L_9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>They had not been long seated and composed when Mr. Woodhouse, with a melancholy shake of the head and a sigh, called his daughter's attention to the sad change at Hartfield since she had been there last.</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>The beginning, however, of every visit displayed none but the properest feelings, and this being of necessity so short might be hoped to pass away in unsullied cordiality. They had not been long seated and composed when Mr. Woodhouse, with a melancholy shake of the head and a sigh, called his daughter's attention to the sad change at Hartfield since she had been there last. "Ah, my dear," said he, "poor Miss Taylor</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>.</t>
@@ -1158,78 +1203,83 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>shake, head, sigh, daughter, attention, change</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>melancholy, sad, last</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>seated, composed, called</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>long, there</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>with, of, to, at</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>ausen-emma_S_39630_L_10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>"I am sorry to hear you say so, sir; but I assure you, excepting those little nervous head-aches and palpitations which I am never entirely free from anywhere, I am quite well myself; and if the children were rather pale before they went to bed, it was only because they were a little more tired than usual, from their journey and the happiness of coming.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Now I cannot say, that I think you are any of you looking well at present." "I am sorry to hear you say so, sir; but I assure you, excepting those little nervous head-aches and palpitations which I am never entirely free from anywhere, I am quite well myself; and if the children were rather pale before they went to bed, it was only because they were a little more tired than usual, from their journey and the happiness of coming. I hope you will think better of their looks to-morrow; for I assure you Mr. Wingfield told me, that he did not believe he had ever sent us off altogether, in such good case.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>.</t>
@@ -1237,78 +1287,83 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>head, aches, palpitations, children, bed, journey, happiness</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>sorry, little, nervous, free, pale, tired, usual</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>hear, say, assure, excepting, went, coming</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>so, never, entirely, anywhere, quite, well, rather, only, little, more</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>from, to, than, from, of</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>ausen-emma_S_40374_L_11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>"Ah!" said Mr. Woodhouse, shaking his head and fixing his eyes on her with tender concern.</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Here was a dangerous opening. "Ah!" said Mr. Woodhouse, shaking his head and fixing his eyes on her with tender concern. The ejaculation in Emma's ear expressed, "Ah! there is no end of the sad consequences of your going to South End.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>.</t>
@@ -1316,70 +1371,75 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>head, eyes, tender, concern</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>said, shaking, fixing</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
         <is>
           <t>on, with</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>ausen-emma_S_41464_L_12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>How they were all to be conveyed, he would have made a difficulty if he could, but as his son and daughter's carriage and horses were actually at Hartfield, he was not able to make more than a simple question on that head; it hardly amounted to a doubt; nor did it occupy Emma long to convince him that they might in one of the carriages find room for Harriet also.</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Mr. Weston would take no denial; they must all dine at Randalls one day; even Mr. Woodhouse was persuaded to think it a possible thing in preference to a division of the party. How they were all to be conveyed, he would have made a difficulty if he could, but as his son and daughter's carriage and horses were actually at Hartfield, he was not able to make more than a simple question on that head; it hardly amounted to a doubt; nor did it occupy Emma long to convince him that they might in one of the carriages find room for Harriet also. Harriet, Mr. Elton, and Mr. Knightley, their own especial set, were the only persons invited to meet them; the hours were to be early, as well as the numbers few; Mr. Woodhouse's habits and inclination being consulted in every thing.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>.</t>
@@ -1387,78 +1447,83 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>difficulty, son, daughter, carriage, horses, question, head, doubt, carriages, room</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>able, more, simple</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>conveyed, made, make, amounted, occupy, convince, find</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>all, actually, hardly, long, also</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>at, than, on, to, in, of, for</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>ausen-emma_S_52610_L_13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>But he had fancied her in love with him; that evidently must have been his dependence; and after raving a little about the seeming incongruity of gentle manners and a conceited head, Emma was obliged in common honesty to stop and admit that her own behaviour to him had been so complaisant and obliging, so full of courtesy and attention, as (supposing her real motive unperceived) might warrant a man of ordinary observation and delicacy, like Mr. Elton, in fancying himself a very decided favourite.</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>The landed property of Hartfield certainly was inconsiderable, being but a sort of notch in the Donwell Abbey estate, to which all the rest of Highbury belonged; but their fortune, from other sources, was such as to make them scarcely secondary to Donwell Abbey itself, in every other kind of consequence; and the Woodhouses had long held a high place in the consideration of the neighbourhood which Mr. Elton had first entered not two years ago, to make his way as he could, without any alliances but in trade, or any thing to recommend him to notice but his situation and his civility. But he had fancied her in love with him; that evidently must have been his dependence; and after raving a little about the seeming incongruity of gentle manners and a conceited head, Emma was obliged in common honesty to stop and admit that her own behaviour to him had been so complaisant and obliging, so full of courtesy and attention, as (supposing her real motive unperceived) might warrant a man of ordinary observation and delicacy, like Mr. Elton, in fancying himself a very decided favourite. If she had so misinterpreted his feelings, she had little right to wonder that he , with self-interest to blind him, should have mistaken hers.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>.</t>
@@ -1466,157 +1531,167 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>love, dependence, incongruity, manners, head, honesty, behaviour, courtesy, attention, motive, man, observation, delicacy</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>little, gentle, conceited, common, own, complaisant, obliging, full, real, ordinary, favourite</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>fancied, raving, seeming, obliged, stop, admit, supposing, unperceived, warrant, fancying, decided</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>evidently, so, so, very</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>in, with, after, about, of, in, to, of, of, like, in</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>ausen-emma_S_68950_L_14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Harriet said, "very true," and she "would not think about it;" but still she talked of it still she could talk of nothing else; and Emma, at last, in order to put the Martins out of her head, was obliged to hurry on the news, which she had meant to give with so much tender caution; hardly knowing herself whether to rejoice or be angry, ashamed or only amused, at such a state of mind in poor Harriet such a conclusion of Mr. Elton's importance with her!</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>She exerted herself, and did try to make her comfortable, by considering all that had passed as a mere trifle, and quite unworthy of being dwelt on, "It might be distressing, for the moment," said she; "but you seem to have behaved extremely well; and it is over and may never can never, as a first meeting, occur again, and therefore you need not think about it." Harriet said, "very true," and she "would not think about it;" but still she talked of it still she could talk of nothing else; and Emma, at last, in order to put the Martins out of her head, was obliged to hurry on the news, which she had meant to give with so much tender caution; hardly knowing herself whether to rejoice or be angry, ashamed or only amused, at such a state of mind in poor Harriet such a conclusion of Mr. Elton's importance with her! Mr. Elton's rights, however, gradually revived.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>order, Martins, head, news, caution, state, mind, conclusion, importance</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>true, last, much, tender, angry, ashamed, poor</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>said, think, talked, talk, put, obliged, hurry, meant, give, knowing, rejoice, amused</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>very, still, still, else, so, hardly, only</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>about, of, of, at, in, out, of, on, with, at, of, in, of, with</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>ausen-emma_S_76580_L_15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>He shook his head and laughed.</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>At least you admire her except her complexion." He shook his head and laughed. "I cannot separate Miss Fairfax and her complexion."</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>.</t>
@@ -1624,41 +1699,45 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>shook, laughed</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -1667,23 +1746,24 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>ausen-emma_S_83449_L_16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>"Yes, and what you told me on that head, confirmed an idea which I had entertained before.</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>We were speaking the other day, you know, of his being so warm an admirer of her performance." "Yes, and what you told me on that head, confirmed an idea which I had entertained before. I do not mean to reflect upon the good intentions of either Mr. Dixon or Miss Fairfax, but I cannot help suspecting either that, after making his proposals to her friend, he had the misfortune to fall in love with her , or that he became conscious of a little attachment on her side.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>.</t>
@@ -1691,74 +1771,79 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>head, idea</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>told, confirmed, entertained</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>before</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>ausen-emma_S_86346_L_17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>"Well," said Mrs. Weston, smiling, "you give him credit for more simple, disinterested benevolence in this instance than I do; for while Miss Bates was speaking, a suspicion darted into my head, and I have never been able to get it out again.</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>I know he had horses to-day for we arrived together; and I laughed at him about it, but he said not a word that could betray." "Well," said Mrs. Weston, smiling, "you give him credit for more simple, disinterested benevolence in this instance than I do; for while Miss Bates was speaking, a suspicion darted into my head, and I have never been able to get it out again. The more I think of it, the more probable it appears.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>.</t>
@@ -1766,78 +1851,83 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>credit, benevolence, instance, suspicion, head</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>simple, disinterested, able</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>said, smiling, give, do, speaking, darted, get</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>more, never, again</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>for, in, for, into, out</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>ausen-emma_S_86843_L_18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Do not put it into his head.</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>I am sure he has not the least idea of it. Do not put it into his head. Why should he marry?</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>.</t>
@@ -1845,70 +1935,75 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>put</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
         <is>
           <t>into</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>ausen-emma_S_93472_L_19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>He shook his head with a smile, and looked as if he had very little doubt and very little mercy.</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Do not distress her." He shook his head with a smile, and looked as if he had very little doubt and very little mercy. Soon afterwards he began again, "How much your friends in Ireland must be enjoying your pleasure on this occasion, Miss Fairfax.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>.</t>
@@ -1916,78 +2011,83 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>head, smile, doubt, mercy</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>little, little</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>shook, looked, had</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>very, very</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>with</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>ausen-emma_S_94613_L_20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>But Emma still shook her head in steady scepticism.</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>The listeners were amused; and Mrs. Weston gave Emma a look of particular meaning. But Emma still shook her head in steady scepticism. "So obliged to you!</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>.</t>
@@ -1995,153 +2095,163 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>head, scepticism</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>steady</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>shook</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>still</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>in</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>ausen-emma_S_100395_L_21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>"Ah! (shaking his head) the uncertainty of when I may be able to return!</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>"This will not be your only visit to Randalls." "Ah! (shaking his head) the uncertainty of when I may be able to return! I shall try for it with a zeal!</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>head, uncertainty</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>able</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>shaking, return</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
         <is>
           <t>of</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>ausen-emma_S_102584_L_22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>When his letter to Mrs. Weston arrived, Emma had the perusal of it; and she read it with a degree of pleasure and admiration which made her at first shake her head over her own sensations, and think she had undervalued their strength.</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>I shall do very well again after a little while and then, it will be a good thing over; for they say every body is in love once in their lives, and I shall have been let off easily." When his letter to Mrs. Weston arrived, Emma had the perusal of it; and she read it with a degree of pleasure and admiration which made her at first shake her head over her own sensations, and think she had undervalued their strength. It was a long, well-written letter, giving the particulars of his journey and of his feelings, expressing all the affection, gratitude, and respect which was natural and honourable, and describing every thing exterior and local that could be supposed attractive, with spirit and precision.</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>.</t>
@@ -2149,78 +2259,83 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>letter, perusal, degree, pleasure, admiration, head, sensations, strength</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>own</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>arrived, had, read, made, shake, think, undervalued</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>to, of, with, of, at, over</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>ausen-emma_S_104031_L_23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Warmth and tenderness of heart, with an affectionate, open manner, will beat all the clearness of head in the world, for attraction, I am sure it will.</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>"There is nothing to be compared to it. Warmth and tenderness of heart, with an affectionate, open manner, will beat all the clearness of head in the world, for attraction, I am sure it will. It is tenderness of heart which makes my dear father so generally beloved which gives Isabella all her popularity.</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>.</t>
@@ -2228,74 +2343,79 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Warmth, tenderness, heart, manner, clearness, head, world, attraction</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>affectionate, open, sure</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>beat</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
         <is>
           <t>of, with, of, in, for</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>ausen-emma_S_104106_L_24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>I would not change you for the clearest-headed, longest-sighted, best-judging female breathing.</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Dear Harriet! I would not change you for the clearest-headed, longest-sighted, best-judging female breathing. Oh!</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>.</t>
@@ -2303,78 +2423,83 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>breathing</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>longest, female</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>change, headed, sighted, judging</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>clearest, best</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>for</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>ausen-emma_S_107310_L_25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>"No, indeed, I have no doubts at all on that head.</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>"We cannot suppose," said Emma, smiling, "that Mr. Elton would hesitate to assure you of there being a very musical society in Highbury; and I hope you will not find he has outstepped the truth more than may be pardoned, in consideration of the motive." "No, indeed, I have no doubts at all on that head. I am delighted to find myself in such a circle.</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>.</t>
@@ -2382,74 +2507,79 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>doubts, head</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>have</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>indeed, at, all</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>ausen-emma_S_112173_L_26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>No till Cole alluded to my supposed attachment, it had never entered my head.</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>She is reserved, more reserved, I think, than she used to be And I love an open temper. No till Cole alluded to my supposed attachment, it had never entered my head. I saw Jane Fairfax and conversed with her, with admiration and pleasure always but with no thought beyond."</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>.</t>
@@ -2457,149 +2587,159 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>attachment, head</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>alluded, supposed, entered</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>never</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>ausen-emma_S_116281_L_27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>"I not aware!" said Jane, shaking her head; "dear Mrs. Elton, who can have thought of it as I have done?"</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>my dear, we cannot begin too early; you are not aware of the difficulty of procuring exactly the desirable thing." "I not aware!" said Jane, shaking her head; "dear Mrs. Elton, who can have thought of it as I have done?" "But you have not seen so much of the world as I have.</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>aware, dear</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>said, shaking, thought, done</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
         <is>
           <t>of</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>ausen-emma_S_119658_L_28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>"She has taken it into her head that Enscombe is too cold for her.</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>To Bath, or to Clifton?" "She has taken it into her head that Enscombe is too cold for her. The fact is, I suppose, that she is tired of Enscombe.</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>.</t>
@@ -2607,78 +2747,83 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>taken</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>too</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>into, for</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>ausen-emma_S_126934_L_29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>She was not yet dancing; she was working her way up from the bottom, and had therefore leisure to look around, and by only turning her head a little she saw it all.</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Emma saw it. She was not yet dancing; she was working her way up from the bottom, and had therefore leisure to look around, and by only turning her head a little she saw it all. When she was half-way up the set, the whole group were exactly behind her, and she would no longer allow her eyes to watch; but Mr. Elton was so near, that she heard every syllable of a dialogue which just then took place between him and Mrs. Weston; and she perceived that his wife, who was standing immediately above her, was not only listening also, but even encouraging him by significant glances.</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>.</t>
@@ -2686,78 +2831,83 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>way, bottom, leisure, head</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>little</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>dancing, working, had, look, turning, saw</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>yet, up, therefore, around, only</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>from, by</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>ausen-emma_S_128454_L_30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>He shook his head; but there was a smile of indulgence with it, and he only said, "I shall not scold you.</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>"I did," replied Emma, "and they cannot forgive me." He shook his head; but there was a smile of indulgence with it, and he only said, "I shall not scold you. I leave you to your own reflections."</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>.</t>
@@ -2765,74 +2915,79 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>head, smile, indulgence</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
         <is>
           <t>shook, was, said, scold</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>only</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>of, with</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>ausen-emma_S_129603_L_31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>How the trampers might have behaved, had the young ladies been more courageous, must be doubtful; but such an invitation for attack could not be resisted; and Harriet was soon assailed by half a dozen children, headed by a stout woman and a great boy, all clamorous, and impertinent in look, though not absolutely in word.</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>She had suffered very much from cramp after dancing, and her first attempt to mount the bank brought on such a return of it as made her absolutely powerless and in this state, and exceedingly terrified, she had been obliged to remain. How the trampers might have behaved, had the young ladies been more courageous, must be doubtful; but such an invitation for attack could not be resisted; and Harriet was soon assailed by half a dozen children, headed by a stout woman and a great boy, all clamorous, and impertinent in look, though not absolutely in word. More and more frightened, she immediately promised them money, and taking out her purse, gave them a shilling, and begged them not to want more, or to use her ill.</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>.</t>
@@ -2840,153 +2995,163 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>trampers, ladies, invitation, attack, dozen, children, woman, boy, look, word</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>young, courageous, doubtful, stout, great, clamorous</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>behaved, had, resisted, assailed, headed, impertinent</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>more, soon, all, absolutely</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>for, by, by, in, in</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>ausen-emma_S_136556_L_32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>And how could it possibly come into your head?"</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>she cried with a most open eagerness "Never, for the twentieth part of a moment, did such an idea occur to me. And how could it possibly come into your head?" "I have lately imagined that I saw symptoms of attachment between them certain expressive looks, which I did not believe meant to be public."</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
         <is>
           <t>come</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>possibly</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>into</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>ausen-emma_S_149874_L_33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>And poor John's son came to talk to Mr. Elton about relief from the parish; he is very well to do himself, you know, being head man at the Crown, ostler, and every thing of that sort, but still he cannot keep his father without some help; and so, when Mr. Elton came back, he told us what John ostler had been telling him, and then it came out about the chaise having been sent to Randalls to take Mr. Frank Churchill to Richmond.</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Poor old John, I have a great regard for him; he was clerk to my poor father twenty-seven years; and now, poor old man, he is bed-ridden, and very poorly with the rheumatic gout in his joints I must go and see him to-day; and so will Jane, I am sure, if she gets out at all. And poor John's son came to talk to Mr. Elton about relief from the parish; he is very well to do himself, you know, being head man at the Crown, ostler, and every thing of that sort, but still he cannot keep his father without some help; and so, when Mr. Elton came back, he told us what John ostler had been telling him, and then it came out about the chaise having been sent to Randalls to take Mr. Frank Churchill to Richmond. That was what happened before tea.</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>.</t>
@@ -2994,78 +3159,83 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>son, relief, head, man, ostler, thing, sort, father, help, ostler, chaise</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>poor, well</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>came, talk, do, know, keep, came, told, telling, came, sent, take</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>very, still, so, back, then</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>to, about, from, at, of, without, out, about, to, to</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>ausen-emma_S_150755_L_34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Emma's colour was heightened by this unjust praise; and with a smile, and shake of the head, which spoke much, she looked at Mr. Knightley.</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>She is always so attentive to them!" Emma's colour was heightened by this unjust praise; and with a smile, and shake of the head, which spoke much, she looked at Mr. Knightley. It seemed as if there were an instantaneous impression in her favour, as if his eyes received the truth from her's, and all that had passed of good in her feelings were at once caught and honoured.</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>.</t>
@@ -3073,78 +3243,83 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>colour, praise, smile, shake, head</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>unjust</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>heightened, spoke, looked</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>much</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>by, with, of, at</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>ausen-emma_S_151760_L_35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>Even Mr. Weston shook his head, and looked solemn, and said, "Ah! poor woman, who would have thought it!" and resolved, that his mourning should be as handsome as possible; and his wife sat sighing and moralising over her broad hems with a commiseration and good sense, true and steady.</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Mr. Churchill would never get over it." Even Mr. Weston shook his head, and looked solemn, and said, "Ah! poor woman, who would have thought it!" and resolved, that his mourning should be as handsome as possible; and his wife sat sighing and moralising over her broad hems with a commiseration and good sense, true and steady. How it would affect Frank was among the earliest thoughts of both.</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>.</t>
@@ -3152,78 +3327,83 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>head, woman, mourning, wife, hems, commiseration, sense</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>solemn, !, poor, handsome, possible, broad, good, true, steady</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>shook, looked, said, thought, resolved, sat, sighing, moralising</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Even, as</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>as, over, with</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>ausen-emma_S_156585_L_36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>"I am quite easy on that head," replied Mrs. Weston.</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>They must take the consequence, if they have heard each other spoken of in a way not perfectly agreeable!" "I am quite easy on that head," replied Mrs. Weston. "I am very sure that I never said any thing of either to the other, which both might not have heard."</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>.</t>
@@ -3231,149 +3411,159 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>replied</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>quite</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>ausen-emma_S_161276_L_37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>The blunders, the blindness of her own head and heart!</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>How to understand the deceptions she had been thus practising on herself, and living under! The blunders, the blindness of her own head and heart! she sat still, she walked about, she tried her own room, she tried the shrubbery in every place, every posture, she perceived that she had acted most weakly; that she had been imposed on by others in a most mortifying degree; that she had been imposing on herself in a degree yet more mortifying; that she was wretched, and should probably find this day but the beginning of wretchedness.</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>blunders, blindness, head, heart</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>own</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
         <is>
           <t>of</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>ausen-emma_S_174778_L_38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>When he came to Miss Woodhouse, he was obliged to read the whole of it aloud all that related to her, with a smile; a look; a shake of the head; a word or two of assent, or disapprobation; or merely of love, as the subject required; concluding, however, seriously, and, after steady reflection, thus "Very bad though it might have been worse.</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>"I was not quite impartial in my judgment, Emma: but yet, I think had you not been in the case I should still have distrusted him." When he came to Miss Woodhouse, he was obliged to read the whole of it aloud all that related to her, with a smile; a look; a shake of the head; a word or two of assent, or disapprobation; or merely of love, as the subject required; concluding, however, seriously, and, after steady reflection, thus "Very bad though it might have been worse. Playing a most dangerous game.</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>.</t>
@@ -3381,78 +3571,83 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>whole, smile, look, shake, head, word, assent, disapprobation, love, subject, reflection</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>steady, bad, worse</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>came, obliged, read, related, required, concluding</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>aloud, merely, however, seriously, thus, Very</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>to, of, to, with, of, of, of, after</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>ausen-emma_S_178199_L_39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>And again, on Emma's merely turning her head to look at Mrs. Bates's knitting, she added, in a half whisper, "I mentioned no names , you will observe.</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>My representation, you see, has quite appeased her." And again, on Emma's merely turning her head to look at Mrs. Bates's knitting, she added, in a half whisper, "I mentioned no names , you will observe. Oh!</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>.</t>
@@ -3460,74 +3655,79 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>head, knitting, half, whisper, names</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
         <is>
           <t>turning, look, added, mentioned, observe</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>again, merely</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>on, at, in</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>ausen-emma_S_186688_L_40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>"Me!" cried Emma, shaking her head.</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Much of this, I have no doubt, she may thank you for." "Me!" cried Emma, shaking her head. "Ah! poor Harriet!"</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>.</t>
@@ -3535,41 +3735,45 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
         <is>
           <t>cried, shaking</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
@@ -3578,23 +3782,24 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>ausen-emma_S_188417_L_41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>You will be glad to hear (inclining his head, and whispering seriously) that my uncle means to give her all my aunt's jewels.</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Observe her eyes, as she is looking up at my father. You will be glad to hear (inclining his head, and whispering seriously) that my uncle means to give her all my aunt's jewels. They are to be new set.</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>.</t>
@@ -3602,50 +3807,54 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>head, uncle, aunt, jewels</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>glad</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>hear, inclining, whispering, means, give</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>seriously</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -3653,23 +3862,24 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>ausen-emma_S_188454_L_42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>I am resolved to have some in an ornament for the head.</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>They are to be new set. I am resolved to have some in an ornament for the head. Will not it be beautiful in her dark hair?"</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>.</t>
@@ -3677,70 +3887,75 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>austen-emma.txt</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>ornament, head</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
         <is>
           <t>resolved, have</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
         <is>
           <t>in, for</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_835_L_1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>This friend, and Sir Walter, did not marry, whatever might have been anticipated on that head by their acquaintance.</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>She had, however, one very intimate friend, a sensible, deserving woman, who had been brought, by strong attachment to herself, to settle close by her, in the village of Kellynch; and on her kindness and advice, Lady Elliot mainly relied for the best help and maintenance of the good principles and instruction which she had been anxiously giving her daughters. This friend, and Sir Walter, did not marry, whatever might have been anticipated on that head by their acquaintance. Thirteen years had passed away since Lady Elliot's death, and they were still near neighbours and intimate friends, and one remained a widower, the other a widow.</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>.</t>
@@ -3748,228 +3963,243 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>friend, head, acquaintance</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
         <is>
           <t>marry, anticipated</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
         <is>
           <t>on, by</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_2124_L_2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>As the head of the house, he felt that he ought to have been consulted, especially after taking the young man so publicly by the hand; "For they must have been seen together," he observed, "once at Tattersall's, and twice in the lobby of the House of Commons."</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Sir Walter has resented it. As the head of the house, he felt that he ought to have been consulted, especially after taking the young man so publicly by the hand; "For they must have been seen together," he observed, "once at Tattersall's, and twice in the lobby of the House of Commons." His disapprobation was expressed, but apparently very little regarded.</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>head, house, man, hand, lobby</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>young</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>felt, consulted, taking, seen, observed</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>especially, so, publicly, together, once, twice</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>As, of, after, by, at, in, of, of</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_3785_L_3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>We must be serious and decided; for after all, the person who has contracted debts must pay them; and though a great deal is due to the feelings of the gentleman, and the head of a house, like your father, there is still more due to the character of an honest man."</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>I have great hope of prevailing. We must be serious and decided; for after all, the person who has contracted debts must pay them; and though a great deal is due to the feelings of the gentleman, and the head of a house, like your father, there is still more due to the character of an honest man." This was the principle on which Anne wanted her father to be proceeding, his friends to be urging him.</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>person, debts, deal, feelings, gentleman, head, house, father, character, man</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>serious, great, due, due, honest</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>decided, contracted, pay, is</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>after, all, still, more</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>for, to, of, of, like, to, of</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_4799_L_4</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>He was not only to quit his home, but to see it in the hands of others; a trial of fortitude, which stronger heads than Sir Walter's have found too much.</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>The undesirableness of any other house in the same neighbourhood for Sir Walter was certainly much strengthened by one part, and a very material part of the scheme, which had been happily engrafted on the beginning. He was not only to quit his home, but to see it in the hands of others; a trial of fortitude, which stronger heads than Sir Walter's have found too much. Kellynch Hall was to be let.</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>.</t>
@@ -3977,390 +4207,415 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>home, hands, others, trial, fortitude, heads</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>stronger, much</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>quit, see, found</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>only, too</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>in, of, of, than</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_6804_L_5</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>It is a pity they are not knocked on the head at once, before they reach Admiral Baldwin's age."</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>I never saw quite so wretched an example of what a sea-faring life can do; but to a degree, I know it is the same with them all: they are all knocked about, and exposed to every climate, and every weather, till they are not fit to be seen. It is a pity they are not knocked on the head at once, before they reach Admiral Baldwin's age." "Nay, Sir Walter," cried Mrs Clay, "this is being severe indeed.</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>pity, head, age</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
         <is>
           <t>knocked, reach</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>once</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>on, at</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_17778_L_6</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>She was quite easy on that head, and consequently full of strength and courage, till for a moment electrified by Mrs Croft's suddenly saying, "It was you, and not your sister, I find, that my brother had the pleasure of being acquainted with, when he was in this country."</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Anne gave her credit, indeed, for feelings of great consideration towards herself, in all that related to Kellynch, and it pleased her: especially, as she had satisfied herself in the very first half minute, in the instant even of introduction, that there was not the smallest symptom of any knowledge or suspicion on Mrs Croft's side, to give a bias of any sort. She was quite easy on that head, and consequently full of strength and courage, till for a moment electrified by Mrs Croft's suddenly saying, "It was you, and not your sister, I find, that my brother had the pleasure of being acquainted with, when he was in this country." Anne hoped she had outlived the age of blushing; but the age of emotion she certainly had not.</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>head, strength, courage, moment, sister, brother, pleasure, country</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>easy, full</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>electrified, saying, find, had, acquainted</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>quite, consequently, suddenly</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>on, of, for, by, of, with, in</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_18393_L_7</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>When the Crofts called this morning, (they called here afterwards, did not they?), they happened to say, that her brother, Captain Wentworth, is just returned to England, or paid off, or something, and is coming to see them almost directly; and most unluckily it came into mamma's head, when they were gone, that Wentworth, or something very like it, was the name of poor Richard's captain at one time; I do not know when or where, but a great while before he died, poor fellow!</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>I will tell you why she is out of spirits. When the Crofts called this morning, (they called here afterwards, did not they?), they happened to say, that her brother, Captain Wentworth, is just returned to England, or paid off, or something, and is coming to see them almost directly; and most unluckily it came into mamma's head, when they were gone, that Wentworth, or something very like it, was the name of poor Richard's captain at one time; I do not know when or where, but a great while before he died, poor fellow! And upon looking over his letters and things, she found it was so, and is perfectly sure that this must be the very man, and her head is quite full of it, and of poor Richard!</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Crofts, morning, brother, head, name, captain, time, while, fellow</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>poor, great, poor</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>called, called, did, happened, say, returned, paid, coming, see, came, gone, know, died</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>here, afterwards, just, almost, directly, most, unluckily, very</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>to, off, into, like, of, at</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_18469_L_8</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>And upon looking over his letters and things, she found it was so, and is perfectly sure that this must be the very man, and her head is quite full of it, and of poor Richard!</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>When the Crofts called this morning, (they called here afterwards, did not they?), they happened to say, that her brother, Captain Wentworth, is just returned to England, or paid off, or something, and is coming to see them almost directly; and most unluckily it came into mamma's head, when they were gone, that Wentworth, or something very like it, was the name of poor Richard's captain at one time; I do not know when or where, but a great while before he died, poor fellow! And upon looking over his letters and things, she found it was so, and is perfectly sure that this must be the very man, and her head is quite full of it, and of poor Richard! So we must be as merry as we can, that she may not be dwelling upon such gloomy things."</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>letters, things, man, head</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>sure, very, full, poor</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>looking, found</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>so, perfectly, quite</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>over, of, of</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_19932_L_9</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>And in short, he had looked and said everything with such exquisite grace, that they could assure them all, their heads were both turned by him; and off they ran, quite as full of glee as of love, and apparently more full of Captain Wentworth than of little Charles.</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>How glad they had been to hear papa invite him to stay dinner, how sorry when he said it was quite out of his power, and how glad again when he had promised in reply to papa and mamma's farther pressing invitations to come and dine with them on the morrow actually on the morrow; and he had promised it in so pleasant a manner, as if he felt all the motive of their attention just as he ought. And in short, he had looked and said everything with such exquisite grace, that they could assure them all, their heads were both turned by him; and off they ran, quite as full of glee as of love, and apparently more full of Captain Wentworth than of little Charles. The same story and the same raptures were repeated, when the two girls came with their father, through the gloom of the evening, to make enquiries; and Mr Musgrove, no longer under the first uneasiness about his heir, could add his confirmation and praise, and hope there would be now no occasion for putting Captain Wentworth off, and only be sorry to think that the cottage party, probably, would not like to leave the little boy, to give him the meeting.</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>.</t>
@@ -4368,78 +4623,83 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>grace, heads, glee, love</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>short, such, exquisite, full, full, little</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>looked, said, assure, turned, ran</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>off, quite, apparently, more</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>in, with, by, as, of, as, of, of, than, of</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_23012_L_10</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>He was rich, and being turned on shore, fully intended to settle as soon as he could be properly tempted; actually looking round, ready to fall in love with all the speed which a clear head and a quick taste could allow.</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>It was now his object to marry. He was rich, and being turned on shore, fully intended to settle as soon as he could be properly tempted; actually looking round, ready to fall in love with all the speed which a clear head and a quick taste could allow. He had a heart for either of the Miss Musgroves, if they could catch it; a heart, in short, for any pleasing young woman who came in his way, excepting Anne Elliot.</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>.</t>
@@ -4447,78 +4707,83 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>shore, love, speed, head, taste</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>rich, round, ready, clear, quick</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>turned, intended, settle, tempted, looking, fall, allow</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>fully, as, soon, properly, actually</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>on, in, with</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_28878_L_11</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>"Charles may say what he pleases," cried Mary to Anne, as soon as he was out of the room, "but it would be shocking to have Henrietta marry Charles Hayter; a very bad thing for her, and still worse for me; and therefore it is very much to be wished that Captain Wentworth may soon put him quite out of her head, and I have very little doubt that he has.</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>No, no; Henrietta might do worse than marry Charles Hayter; and if she has him, and Louisa can get Captain Wentworth, I shall be very well satisfied." "Charles may say what he pleases," cried Mary to Anne, as soon as he was out of the room, "but it would be shocking to have Henrietta marry Charles Hayter; a very bad thing for her, and still worse for me; and therefore it is very much to be wished that Captain Wentworth may soon put him quite out of her head, and I have very little doubt that he has. She took hardly any notice of Charles Hayter yesterday.</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>.</t>
@@ -4526,78 +4791,83 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>room, thing, head, doubt</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>shocking, bad, worse, little</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>say, pleases, cried, have, marry, wished, put, have</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>as, soon, very, still, therefore, very, much, soon, quite, very</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>to, out, of, for, for, out, of</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_29882_L_12</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>She hoped, on turning her head, to see the master of the house; but it proved to be one much less calculated for making matters easy Charles Hayter, probably not at all better pleased by the sight of Captain Wentworth than Captain Wentworth had been by the sight of Anne.</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>She was obliged to kneel down by the sofa, and remain there to satisfy her patient; and thus they continued a few minutes, when, to her very great satisfaction, she heard some other person crossing the little vestibule. She hoped, on turning her head, to see the master of the house; but it proved to be one much less calculated for making matters easy Charles Hayter, probably not at all better pleased by the sight of Captain Wentworth than Captain Wentworth had been by the sight of Anne. She only attempted to say, "How do you do?</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>.</t>
@@ -4605,78 +4875,83 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>head, master, house, matters, sight, sight</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>easy, pleased</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>hoped, turning, see, proved, calculated, making</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>much, less, probably, at, all, better</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>on, of, for, by, of, than, by, of</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_30275_L_13</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>In another moment, however, she found herself in the state of being released from him; some one was taking him from her, though he had bent down her head so much, that his little sturdy hands were unfastened from around her neck, and he was resolutely borne away, before she knew that Captain Wentworth had done it.</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>But not a bit did Walter stir. In another moment, however, she found herself in the state of being released from him; some one was taking him from her, though he had bent down her head so much, that his little sturdy hands were unfastened from around her neck, and he was resolutely borne away, before she knew that Captain Wentworth had done it. Her sensations on the discovery made her perfectly speechless.</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>.</t>
@@ -4684,78 +4959,83 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>moment, state, one, head, hands, neck</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>little, sturdy</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>found, released, taking, bent, unfastened, borne, knew, done</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>however, so, much, resolutely, away</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>In, in, of, from, from, down, from, around</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_34068_L_14</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>Mary had shewn herself disobliging to him, and was now to reap the consequence, which consequence was his dropping her arm almost every moment to cut off the heads of some nettles in the hedge with his switch; and when Mary began to complain of it, and lament her being ill-used, according to custom, in being on the hedge side, while Anne was never incommoded on the other, he dropped the arms of both to hunt after a weasel which he had a momentary glance of, and they could hardly get him along at all.</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>She joined Charles and Mary, and was tired enough to be very glad of Charles's other arm; but Charles, though in very good humour with her, was out of temper with his wife. Mary had shewn herself disobliging to him, and was now to reap the consequence, which consequence was his dropping her arm almost every moment to cut off the heads of some nettles in the hedge with his switch; and when Mary began to complain of it, and lament her being ill-used, according to custom, in being on the hedge side, while Anne was never incommoded on the other, he dropped the arms of both to hunt after a weasel which he had a momentary glance of, and they could hardly get him along at all. This long meadow bordered a lane, which their footpath, at the end of it was to cross, and when the party had all reached the gate of exit, the carriage advancing in the same direction, which had been some time heard, was just coming up, and proved to be Admiral Croft's gig.</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>.</t>
@@ -4763,78 +5043,83 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>consequence, consequence, arm, moment, heads, nettles, hedge, switch, custom, hedge, side, arms, weasel, glance</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>other, momentary</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>shewn, disobliging, reap, dropping, cut, began, complain, lament, used, according, incommoded, dropped, hunt, had, get</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>now, almost, ill, never, hardly, at, all</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>to, off, of, in, with, of, to, in, on, on, of, after, of, along</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_37838_L_15</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>They went back to dress and dine; and so well had the scheme answered already, that nothing was found amiss; though its being "so entirely out of season," and the "no thoroughfare of Lyme," and the "no expectation of company," had brought many apologies from the heads of the inn.</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Anne thought she left great happiness behind her when they quitted the house; and Louisa, by whom she found herself walking, burst forth into raptures of admiration and delight on the character of the navy; their friendliness, their brotherliness, their openness, their uprightness; protesting that she was convinced of sailors having more worth and warmth than any other set of men in England; that they only knew how to live, and they only deserved to be respected and loved. They went back to dress and dine; and so well had the scheme answered already, that nothing was found amiss; though its being "so entirely out of season," and the "no thoroughfare of Lyme," and the "no expectation of company," had brought many apologies from the heads of the inn. Anne found herself by this time growing so much more hardened to being in Captain Wentworth's company than she had at first imagined could ever be, that the sitting down to the same table with him now, and the interchange of the common civilities attending on it (they never got beyond), was become a mere nothing.</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>.</t>
@@ -4842,78 +5127,83 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>dress, dine, scheme, being, season, thoroughfare, expectation, company, apologies, heads</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>amiss, many</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>went, had, answered, found, brought</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>back, so, well, already, so, entirely</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>to, out, of, of, of, from, of</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_38528_L_16</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Captain Benwick listened attentively, and seemed grateful for the interest implied; and though with a shake of the head, and sighs which declared his little faith in the efficacy of any books on grief like his, noted down the names of those she recommended, and promised to procure and read them.</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>His looks shewing him not pained, but pleased with this allusion to his situation, she was emboldened to go on; and feeling in herself the right of seniority of mind, she ventured to recommend a larger allowance of prose in his daily study; and on being requested to particularize, mentioned such works of our best moralists, such collections of the finest letters, such memoirs of characters of worth and suffering, as occurred to her at the moment as calculated to rouse and fortify the mind by the highest precepts, and the strongest examples of moral and religious endurances. Captain Benwick listened attentively, and seemed grateful for the interest implied; and though with a shake of the head, and sighs which declared his little faith in the efficacy of any books on grief like his, noted down the names of those she recommended, and promised to procure and read them. When the evening was over, Anne could not but be amused at the idea of her coming to Lyme to preach patience and resignation to a young man whom she had never seen before; nor could she help fearing, on more serious reflection, that, like many other great moralists and preachers, she had been eloquent on a point in which her own conduct would ill bear examination.</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>.</t>
@@ -4921,78 +5211,83 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>interest, shake, head, sighs, faith, efficacy, books, grief, names</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>grateful, little</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>listened, seemed, implied, declared, noted, recommended, promised, procure, read</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>attentively</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>with, of, in, of, on, like, down, of</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_42993_L_17</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>The head had received a severe contusion, but he had seen greater injuries recovered from: he was by no means hopeless; he spoke cheerfully.</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>They were sick with horror, while he examined; but he was not hopeless. The head had received a severe contusion, but he had seen greater injuries recovered from: he was by no means hopeless; he spoke cheerfully. That he did not regard it as a desperate case, that he did not say a few hours must end it, was at first felt, beyond the hope of most; and the ecstasy of such a reprieve, the rejoicing, deep and silent, after a few fervent ejaculations of gratitude to Heaven had been offered, may be conceived.</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>.</t>
@@ -5000,78 +5295,83 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>head, contusion, injuries, means</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>severe, greater</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>received, seen, recovered, spoke</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>hopeless, cheerfully</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>from, by</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_43173_L_18</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>There was no injury but to the head.</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Louisa's limbs had escaped. There was no injury but to the head. It now became necessary for the party to consider what was best to be done, as to their general situation.</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>.</t>
@@ -5079,192 +5379,206 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>injury, head</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
         <is>
           <t>was</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_47604_L_19</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>A new sort of way this, for a young fellow to be making love, by breaking his mistress's head, is not it, Miss Elliot?</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>The Admiral wound it up summarily by exclaiming "Ay, a very bad business indeed. A new sort of way this, for a young fellow to be making love, by breaking his mistress's head, is not it, Miss Elliot? This is breaking a head and giving a plaster, truly!"</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>sort, way, fellow, love, mistress, head</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>new, young</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>making, breaking</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
         <is>
           <t>of, for, by</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_47617_L_20</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>This is breaking a head and giving a plaster, truly!"</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>A new sort of way this, for a young fellow to be making love, by breaking his mistress's head, is not it, Miss Elliot? This is breaking a head and giving a plaster, truly!" Admiral Croft's manners were not quite of the tone to suit Lady Russell, but they delighted Anne.</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>head, plaster</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
         <is>
           <t>breaking, giving</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>truly</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
@@ -5272,23 +5586,24 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_48511_L_21</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>They had left Louisa beginning to sit up; but her head, though clear, was exceedingly weak, and her nerves susceptible to the highest extreme of tenderness; and though she might be pronounced to be altogether doing very well, it was still impossible to say when she might be able to bear the removal home; and her father and mother, who must return in time to receive their younger children for the Christmas holidays, had hardly a hope of being allowed to bring her with them.</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Though Charles and Mary had remained at Lyme much longer after Mr and Mrs Musgrove's going than Anne conceived they could have been at all wanted, they were yet the first of the family to be at home again; and as soon as possible after their return to Uppercross they drove over to the Lodge. They had left Louisa beginning to sit up; but her head, though clear, was exceedingly weak, and her nerves susceptible to the highest extreme of tenderness; and though she might be pronounced to be altogether doing very well, it was still impossible to say when she might be able to bear the removal home; and her father and mother, who must return in time to receive their younger children for the Christmas holidays, had hardly a hope of being allowed to bring her with them. They had been all in lodgings together.</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>.</t>
@@ -5296,232 +5611,247 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>head, nerves, extreme, tenderness, removal, home, father, mother, time, children, holidays, hope</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>clear, weak, susceptible, highest, impossible, able, younger</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>left, beginning, sit, pronounced, doing, say, bear, return, receive, had, allowed, bring</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>exceedingly, altogether, very, well, still, hardly</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>up, to, of, in, for, of, with</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_49333_L_22</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>His head is full of some books that he is reading upon your recommendation, and he wants to talk to you about them; he has found out something or other in one of them which he thinks oh!</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>"No," admitted Charles, "I do not know that he ever does, in a general way; but however, it is a very clear thing that he admires you exceedingly. His head is full of some books that he is reading upon your recommendation, and he wants to talk to you about them; he has found out something or other in one of them which he thinks oh! I cannot pretend to remember it, but it was something very fine I overheard him telling Henrietta all about it; and then `Miss Elliot' was spoken of in the highest terms!</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>head, books, recommendation</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>full, other</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>reading, wants, talk, found, thinks</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
         <is>
           <t>of, to, about, out, in, of</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_50144_L_23</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>His declining to be on cordial terms with the head of his family, has left a very strong impression in his disfavour with me."</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>"He is a man," said Lady Russell, "whom I have no wish to see. His declining to be on cordial terms with the head of his family, has left a very strong impression in his disfavour with me." This decision checked Mary's eagerness, and stopped her short in the midst of the Elliot countenance.</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>terms, head, family, impression, disfavour</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>cordial, strong</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>declining, left</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>very</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>on, with, of, in, with</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_50290_L_24</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>He had not seen Louisa; and was so extremely fearful of any ill consequence to her from an interview, that he did not press for it at all; and, on the contrary, seemed to have a plan of going away for a week or ten days, till her head was stronger.</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>As Louisa improved, he had improved, and he was now quite a different creature from what he had been the first week. He had not seen Louisa; and was so extremely fearful of any ill consequence to her from an interview, that he did not press for it at all; and, on the contrary, seemed to have a plan of going away for a week or ten days, till her head was stronger. He had talked of going down to Plymouth for a week, and wanted to persuade Captain Benwick to go with him; but, as Charles maintained to the last, Captain Benwick seemed much more disposed to ride over to Kellynch.</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>.</t>
@@ -5529,78 +5859,83 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>consequence, interview, contrary, plan, week, days, head</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>fearful, ill, stronger</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>seen, press, seemed, have, going</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>so, extremely, at, all, away</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>of, to, from, for, on, of, for</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_55754_L_25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>In Lady Russell's view, it was perfectly natural that Mr Elliot, at a mature time of life, should feel it a most desirable object, and what would very generally recommend him among all sensible people, to be on good terms with the head of his family; the simplest process in the world of time upon a head naturally clear, and only erring in the heyday of youth.</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>It was now some years since Anne had begun to learn that she and her excellent friend could sometimes think differently; and it did not surprise her, therefore, that Lady Russell should see nothing suspicious or inconsistent, nothing to require more motives than appeared, in Mr Elliot's great desire of a reconciliation. In Lady Russell's view, it was perfectly natural that Mr Elliot, at a mature time of life, should feel it a most desirable object, and what would very generally recommend him among all sensible people, to be on good terms with the head of his family; the simplest process in the world of time upon a head naturally clear, and only erring in the heyday of youth. Anne presumed, however, still to smile about it, and at last to mention "Elizabeth."</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>.</t>
@@ -5608,78 +5943,83 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>view, time, life, object, people, terms, head, family, process, world, time, head, heyday, youth</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>natural, mature, desirable, sensible, good, simplest, clear</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>feel, recommend, erring</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>perfectly, most, very, generally, naturally, only</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>In, at, of, among, on, with, of, in, of, in, of</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_55769_L_26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>In Lady Russell's view, it was perfectly natural that Mr Elliot, at a mature time of life, should feel it a most desirable object, and what would very generally recommend him among all sensible people, to be on good terms with the head of his family; the simplest process in the world of time upon a head naturally clear, and only erring in the heyday of youth.</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>It was now some years since Anne had begun to learn that she and her excellent friend could sometimes think differently; and it did not surprise her, therefore, that Lady Russell should see nothing suspicious or inconsistent, nothing to require more motives than appeared, in Mr Elliot's great desire of a reconciliation. In Lady Russell's view, it was perfectly natural that Mr Elliot, at a mature time of life, should feel it a most desirable object, and what would very generally recommend him among all sensible people, to be on good terms with the head of his family; the simplest process in the world of time upon a head naturally clear, and only erring in the heyday of youth. Anne presumed, however, still to smile about it, and at last to mention "Elizabeth."</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>.</t>
@@ -5687,78 +6027,83 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>view, time, life, object, people, terms, head, family, process, world, time, head, heyday, youth</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>natural, mature, desirable, sensible, good, simplest, clear</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>feel, recommend, erring</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>perfectly, most, very, generally, naturally, only</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>In, at, of, among, on, with, of, in, of, in, of</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_56396_L_27</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>The neglect had been visited on the head of the sinner; for when poor Lady Elliot died herself, no letter of condolence was received at Kellynch, and, consequently, there was but too much reason to apprehend that the Dalrymples considered the relationship as closed.</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>No letter of condolence had been sent to Ireland. The neglect had been visited on the head of the sinner; for when poor Lady Elliot died herself, no letter of condolence was received at Kellynch, and, consequently, there was but too much reason to apprehend that the Dalrymples considered the relationship as closed. How to have this anxious business set to rights, and be admitted as cousins again, was the question: and it was a question which, in a more rational manner, neither Lady Russell nor Mr Elliot thought unimportant.</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>.</t>
@@ -5766,78 +6111,83 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>neglect, head, sinner, letter, condolence, reason, relationship</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>poor, much</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>visited, died, received, was, apprehend, considered, closed</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>consequently, too</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>on, of, for, of, at</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_57014_L_28</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>My cousin Anne shakes her head.</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Birth and good manners are essential; but a little learning is by no means a dangerous thing in good company; on the contrary, it will do very well. My cousin Anne shakes her head. She is not satisfied.</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>.</t>
@@ -5845,41 +6195,45 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>cousin, head</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
         <is>
           <t>shakes</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
@@ -5888,23 +6242,24 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_60680_L_29</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>Anne heard her, and made no violent exclamations; she only smiled, blushed, and gently shook her head.</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>She would not speak to Anne with half the certainty she felt on the subject, she would venture on little more than hints of what might be hereafter, of a possible attachment on his side, of the desirableness of the alliance, supposing such attachment to be real and returned. Anne heard her, and made no violent exclamations; she only smiled, blushed, and gently shook her head. "I am no match-maker, as you well know," said Lady Russell, "being much too well aware of the uncertainty of all human events and calculations.</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>.</t>
@@ -5912,50 +6267,54 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>exclamations, head</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>violent</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>heard, made, smiled, blushed, shook</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>only, gently</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
@@ -5963,23 +6322,24 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_63041_L_30</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>How Charles could take such a thing into his head was always incomprehensible to me.</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>And this is the end, you see, of Captain Benwick's being supposed to be an admirer of yours. How Charles could take such a thing into his head was always incomprehensible to me. I hope he will be more agreeable now.</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>.</t>
@@ -5987,78 +6347,83 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>thing, head</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>incomprehensible</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>take</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>always</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>into, to</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_68827_L_31</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>At last, Lady Russell drew back her head.</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>She could thoroughly comprehend the sort of fascination he must possess over Lady Russell's mind, the difficulty it must be for her to withdraw her eyes, the astonishment she must be feeling that eight or nine years should have passed over him, and in foreign climes and in active service too, without robbing him of one personal grace! At last, Lady Russell drew back her head. "Now, how would she speak of him?"</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>.</t>
@@ -6066,228 +6431,243 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="K74" t="inlineStr">
         <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t>last</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>drew</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>back</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>At</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_75032_L_32</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>Mrs Smith looked at her again, looked earnestly, smiled, shook her head, and exclaimed "Now, how I do wish I understood you!</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>I should like to know why you imagine I am?" Mrs Smith looked at her again, looked earnestly, smiled, shook her head, and exclaimed "Now, how I do wish I understood you! How I do wish I knew what you were at!</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
         <is>
           <t>looked, looked, smiled, shook, exclaimed, wish, understood</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>again, earnestly, Now</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_75748_L_33</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>"Do tell me how it first came into your head."</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>As it was, she instantly submitted, and with all the semblance of seeing nothing beyond; and Anne, eager to escape farther notice, was impatient to know why Mrs Smith should have fancied she was to marry Mr Elliot; where she could have received the idea, or from whom she could have heard it. "Do tell me how it first came into your head." "It first came into my head," replied Mrs Smith, "upon finding how much you were together, and feeling it to be the most probable thing in the world to be wished for by everybody belonging to either of you; and you may depend upon it that all your acquaintance have disposed of you in the same way.</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
         <is>
           <t>tell, came</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>first</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>into</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_75757_L_34</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>"It first came into my head," replied Mrs Smith, "upon finding how much you were together, and feeling it to be the most probable thing in the world to be wished for by everybody belonging to either of you; and you may depend upon it that all your acquaintance have disposed of you in the same way.</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>"Do tell me how it first came into your head." "It first came into my head," replied Mrs Smith, "upon finding how much you were together, and feeling it to be the most probable thing in the world to be wished for by everybody belonging to either of you; and you may depend upon it that all your acquaintance have disposed of you in the same way. But I never heard it spoken of till two days ago."</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>.</t>
@@ -6295,157 +6675,167 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>head, thing, world, acquaintance, way</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>probable, same</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>came, replied, finding, feeling, wished, belonging, depend, disposed</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>first, much, together, most</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>into, in, for, by, to, of, of, in</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_88763_L_35</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>He was full of `to-morrow,' and it is very evident that I have been full of it too, ever since I entered the house, and learnt the extension of your plan and all that had happened, or my seeing him could never have gone so entirely out of my head."</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>He wanted to know how early he might be admitted to-morrow. He was full of `to-morrow,' and it is very evident that I have been full of it too, ever since I entered the house, and learnt the extension of your plan and all that had happened, or my seeing him could never have gone so entirely out of my head." Chapter 23 One day only had passed since Anne's conversation with Mrs Smith; but a keener interest had succeeded, and she was now so little touched by Mr Elliot's conduct, except by its effects in one quarter, that it became a matter of course the next morning, still to defer her explanatory visit in Rivers Street.</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>"</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>morrow, house, extension, plan, head</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>full, evident, full</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>entered, learnt, happened, seeing, gone</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>very, too, ever, never, so, entirely</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>of, to, of, of, out, of</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_88859_L_36</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>Her faith was plighted, and Mr Elliot's character, like the Sultaness Scheherazade's head, must live another day.</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>She had promised to be with the Musgroves from breakfast to dinner. Her faith was plighted, and Mr Elliot's character, like the Sultaness Scheherazade's head, must live another day. She could not keep her appointment punctually, however; the weather was unfavourable, and she had grieved over the rain on her friends' account, and felt it very much on her own, before she was able to attempt the walk.</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>.</t>
@@ -6453,70 +6843,75 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>faith, character, head, day</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
         <is>
           <t>plighted, live</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
         <is>
           <t>like</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_89737_L_37</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>She felt its application to herself, felt it in a nervous thrill all over her; and at the same moment that her eyes instinctively glanced towards the distant table, Captain Wentworth's pen ceased to move, his head was raised, pausing, listening, and he turned round the next instant to give a look, one quick, conscious look at her.</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Anne found an unexpected interest here. She felt its application to herself, felt it in a nervous thrill all over her; and at the same moment that her eyes instinctively glanced towards the distant table, Captain Wentworth's pen ceased to move, his head was raised, pausing, listening, and he turned round the next instant to give a look, one quick, conscious look at her. The two ladies continued to talk, to re-urge the same admitted truths, and enforce them with such examples of the ill effect of a contrary practice as had fallen within their observation, but Anne heard nothing distinctly; it was only a buzz of words in her ear, her mind was in confusion.</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>.</t>
@@ -6524,78 +6919,83 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>application, thrill, moment, eyes, table, pen, head, pausing, listening, instant, look, look</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>nervous, same, distant, next, quick, conscious</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>felt, felt, glanced, ceased, move, raised, turned, give</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>all, instinctively, round</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>to, in, over, at, towards, at</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_89894_L_38</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>He looked at her with a smile, and a little motion of the head, which expressed, "Come to me, I have something to say;" and the unaffected, easy kindness of manner which denoted the feelings of an older acquaintance than he really was, strongly enforced the invitation.</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Captain Harville, who had in truth been hearing none of it, now left his seat, and moved to a window, and Anne seeming to watch him, though it was from thorough absence of mind, became gradually sensible that he was inviting her to join him where he stood. He looked at her with a smile, and a little motion of the head, which expressed, "Come to me, I have something to say;" and the unaffected, easy kindness of manner which denoted the feelings of an older acquaintance than he really was, strongly enforced the invitation. She roused herself and went to him.</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D81" t="inlineStr">
         <is>
           <t>.</t>
@@ -6603,78 +7003,83 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>smile, motion, head, kindness, manner, feelings, acquaintance, invitation</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>little, unaffected, easy, older</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>looked, expressed, Come, have, say, denoted, enforced</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>really, strongly</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>at, with, of, to, of, of</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_92943_L_39</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>The chair was earnestly protested against, and Mrs Musgrove, who thought only of one sort of illness, having assured herself with some anxiety, that there had been no fall in the case; that Anne had not at any time lately slipped down, and got a blow on her head; that she was perfectly convinced of having had no fall; could part with her cheerfully, and depend on finding her better at night.</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>To lose the possibility of speaking two words to Captain Wentworth in the course of her quiet, solitary progress up the town (and she felt almost certain of meeting him) could not be borne. The chair was earnestly protested against, and Mrs Musgrove, who thought only of one sort of illness, having assured herself with some anxiety, that there had been no fall in the case; that Anne had not at any time lately slipped down, and got a blow on her head; that she was perfectly convinced of having had no fall; could part with her cheerfully, and depend on finding her better at night. Anxious to omit no possible precaution, Anne struggled, and said "I am afraid, ma'am, that it is not perfectly understood.</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>.</t>
@@ -6682,78 +7087,83 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>chair, sort, illness, anxiety, fall, case, time, blow, head, fall, night</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>convinced, better</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>protested, thought, assured, slipped, got, part, depend, finding</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>earnestly, only, lately, down, perfectly, cheerfully</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>against, of, of, with, in, at, on, of, with, on, at</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>ausen-persuasion_S_96641_L_40</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>When any two young people take it into their heads to marry, they are pretty sure by perseverance to carry their point, be they ever so poor, or ever so imprudent, or ever so little likely to be necessary to each other's ultimate comfort.</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Chapter 24 Who can be in doubt of what followed? When any two young people take it into their heads to marry, they are pretty sure by perseverance to carry their point, be they ever so poor, or ever so imprudent, or ever so little likely to be necessary to each other's ultimate comfort. This may be bad morality to conclude with, but I believe it to be truth; and if such parties succeed, how should a Captain Wentworth and an Anne Elliot, with the advantage of maturity of mind, consciousness of right, and one independent fortune between them, fail of bearing down every opposition?</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>.</t>
@@ -6761,61 +7171,66 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>body part</t>
+          <t>head</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>body part</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>NLTK Gutenberg</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
+          <t>NLTK Gutenberg</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
           <t>austen-persuasion.txt</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>people, heads, perseverance, point, comfort</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>young, sure, poor, imprudent, likely, necessary, other, ultimate</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>take, marry, carry</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>pretty, ever, so, ever, so, ever, so, little</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>into, by, to</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
